--- a/public/data/videoke-musicasV2-generos-revisados.xlsx
+++ b/public/data/videoke-musicasV2-generos-revisados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\01278758\Documents\projetos karaoke\projeto-videoke\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8CB418-FCE8-48EC-9416-01A1E2B045CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCF2037-291C-429C-8491-3B75E03A7693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26059,7 +26059,7 @@
         <v>318</v>
       </c>
       <c r="G218" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
@@ -26082,7 +26082,7 @@
         <v>195</v>
       </c>
       <c r="G219" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
@@ -26105,7 +26105,7 @@
         <v>103</v>
       </c>
       <c r="G220" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
@@ -26128,7 +26128,7 @@
         <v>23</v>
       </c>
       <c r="G221" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
@@ -26151,7 +26151,7 @@
         <v>142</v>
       </c>
       <c r="G222" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
@@ -26174,7 +26174,7 @@
         <v>34</v>
       </c>
       <c r="G223" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
@@ -26197,7 +26197,7 @@
         <v>14</v>
       </c>
       <c r="G224" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
@@ -26220,7 +26220,7 @@
         <v>206</v>
       </c>
       <c r="G225" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
@@ -26243,7 +26243,7 @@
         <v>198</v>
       </c>
       <c r="G226" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
@@ -26266,7 +26266,7 @@
         <v>195</v>
       </c>
       <c r="G227" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
@@ -26289,7 +26289,7 @@
         <v>195</v>
       </c>
       <c r="G228" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
@@ -26312,7 +26312,7 @@
         <v>198</v>
       </c>
       <c r="G229" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
@@ -26335,7 +26335,7 @@
         <v>195</v>
       </c>
       <c r="G230" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
@@ -36118,7 +36118,7 @@
         <v>187</v>
       </c>
       <c r="G659" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.35">
@@ -36141,7 +36141,7 @@
         <v>327</v>
       </c>
       <c r="G660" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.35">
@@ -36164,7 +36164,7 @@
         <v>327</v>
       </c>
       <c r="G661" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.35">
@@ -36187,7 +36187,7 @@
         <v>187</v>
       </c>
       <c r="G662" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.35">
@@ -36210,7 +36210,7 @@
         <v>195</v>
       </c>
       <c r="G663" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.35">
@@ -36233,7 +36233,7 @@
         <v>187</v>
       </c>
       <c r="G664" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.35">
@@ -36256,7 +36256,7 @@
         <v>132</v>
       </c>
       <c r="G665" t="s">
-        <v>6834</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.35">
